--- a/transaction.xlsx
+++ b/transaction.xlsx
@@ -1,58 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gpecheur\AppData\Roaming\QGIS\QGIS3\profiles\default\python\plugins\(IGN)assisstant_dfci\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B07AE8-7C95-4B92-8B00-9D9347F701B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-20130" yWindow="3330" windowWidth="17280" windowHeight="8970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Assisstant DFCI" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assistant DFCI" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>N° de transaction</t>
-  </si>
-  <si>
-    <t>CLEABS</t>
-  </si>
-  <si>
-    <t>Champs modifiés</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -67,49 +45,99 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thick"/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom style="thick"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -397,256 +425,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="100" customWidth="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>N° de transaction</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>CLEABS</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Champs modifiés</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>09 July 2025 15:07</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>En cours de dévo</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>TRONROUT0000000357705887</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">categorie_dfci :NULL ---&gt;1ère catégorie
+</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
